--- a/incident_report_forms/019_pharmaceutical_trial_adverse_event_incident_report--incident_report_forms.xlsx
+++ b/incident_report_forms/019_pharmaceutical_trial_adverse_event_incident_report--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sponsor'}</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sponsor'}</t>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'research_site'}</t>
+          <t>research_site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Research Site'}</t>
+          <t>Research Site</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'investigator'}</t>
+          <t>investigator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Investigator'}</t>
+          <t>Investigator</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'adverse_event'}</t>
+          <t>adverse_event</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Adverse Event'}</t>
+          <t>Adverse Event</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'serious_adverse_event'}</t>
+          <t>serious_adverse_event</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Serious Adverse Event'}</t>
+          <t>Serious Adverse Event</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'serious_and_unexpected_adverse_event'}</t>
+          <t>serious_and_unexpected_adverse_event</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Serious and Unexpected Adverse Event'}</t>
+          <t>Serious and Unexpected Adverse Event</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'unexpected_adverse_event'}</t>
+          <t>unexpected_adverse_event</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Unexpected Adverse Event'}</t>
+          <t>Unexpected Adverse Event</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
